--- a/output/pdf_financials_xlsx/ICWY.P.xlsx
+++ b/output/pdf_financials_xlsx/ICWY.P.xlsx
@@ -2821,16 +2821,16 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.059967</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.059967</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.059967</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.059967</v>
       </c>
     </row>
     <row r="93">
@@ -4176,7 +4176,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>-</t>
@@ -4472,7 +4476,11 @@
           <t>Share-based payment reserve (Note 5)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ICWY.P.xlsx
+++ b/output/pdf_financials_xlsx/ICWY.P.xlsx
@@ -649,22 +649,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>6e-06</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.013082</v>
+        <v>0.053902</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.028843</v>
+        <v>0.107977</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.014493</v>
+        <v>0.056532</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.014237</v>
+        <v>0.025583</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.014648</v>
+        <v>0.027398</v>
       </c>
     </row>
     <row r="11">
@@ -674,22 +674,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>-6e-06</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.013082</v>
+        <v>-0.053902</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.028843</v>
+        <v>-0.107977</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.014493</v>
+        <v>-0.056532</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.014237</v>
+        <v>-0.025583</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.014648</v>
+        <v>-0.027398</v>
       </c>
     </row>
     <row r="12">
@@ -705,16 +705,16 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.00414</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.009878</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.008954999999999999</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.005481</v>
       </c>
     </row>
     <row r="13">
@@ -1118,16 +1118,16 @@
         <v>-0.053902</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.103837</v>
+        <v>-0.107977</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.046654</v>
+        <v>-0.056532</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.016628</v>
+        <v>-0.025583</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.021917</v>
+        <v>-0.027398</v>
       </c>
     </row>
     <row r="28">
@@ -1168,16 +1168,16 @@
         <v>-0.053902</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.103837</v>
+        <v>-0.107977</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.046654</v>
+        <v>-0.056532</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.016628</v>
+        <v>-0.025583</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.021917</v>
+        <v>-0.027398</v>
       </c>
     </row>
     <row r="30">
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.039994</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.135408</v>
@@ -1302,7 +1302,7 @@
         <v>0.284456</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.238159</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0.221887</v>
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.039994</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.135408</v>
@@ -1352,7 +1352,7 @@
         <v>0.284456</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.238159</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0.221887</v>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6970,7 +6970,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">

--- a/output/pdf_financials_xlsx/ICWY.P.xlsx
+++ b/output/pdf_financials_xlsx/ICWY.P.xlsx
@@ -6562,7 +6562,11 @@
           <t>Fair value of agent’s options from private placement</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
